--- a/Project/Solution/Task_5_Inconcistencies_Analysis.xlsx
+++ b/Project/Solution/Task_5_Inconcistencies_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github_windows\DE_CS_202309\Project\Solution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5515ABE-60FC-448A-B6C2-BD3E44342B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA9962B-06C3-4CAF-8FBA-BE55D74B07B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11565" yWindow="1200" windowWidth="31185" windowHeight="19215" xr2:uid="{E28B71DA-33FB-45D9-97D2-4FF5209A988D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E28B71DA-33FB-45D9-97D2-4FF5209A988D}"/>
   </bookViews>
   <sheets>
     <sheet name="Inconsistencies_Summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Inconsistency Type</t>
   </si>
@@ -59,12 +59,6 @@
   </si>
   <si>
     <t>Duplicate Product IDs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There are 1881 unique Product IDs, while 1834 Unique product names. 47 Objects have repeated IDs, which makes Product ID unusable as Primary Key. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">We can consider the combination of Product ID, Category and Sub-Category as Composite key for the product Table. We may also check the same with business if it needs correction. </t>
   </si>
   <si>
     <t xml:space="preserve">Correct the date format if possible, howeverm in the case of ambiguity, we can always refer the business to maintain a strict date format or cleanse it at the source. </t>
@@ -178,6 +172,18 @@
   <si>
     <t xml:space="preserve">The Date format of the Order Dat column was inconsistent with the rest of the data. Also, there are rows which are in mixed DD/MM/YYYY and MM/DD/YYYY format. </t>
   </si>
+  <si>
+    <t xml:space="preserve">5 pair of products have the same ID. In Total, 10 objects have Data consistency isssues. </t>
+  </si>
+  <si>
+    <t>10 Product entries or 5 pair of Products.</t>
+  </si>
+  <si>
+    <t>We need to assign different IDs to each product. In this case, we can check with the ASME/Business for further actions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are user names that have non-standard characters in it. It can cause issues in some cases while filtering or formatting. </t>
+  </si>
 </sst>
 </file>
 
@@ -220,12 +226,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -263,8 +266,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{53DD33C5-2FF4-4D40-B827-D836ACC78D2E}" name="Table1" displayName="Table1" ref="A1:D9" totalsRowShown="0">
   <autoFilter ref="A1:D9" xr:uid="{53DD33C5-2FF4-4D40-B827-D836ACC78D2E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B6B86EFF-FFA0-4D77-AFEA-220F5D28CE3B}" name="Inconsistency Type" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{AA763C70-26AE-4394-9943-58CCD15D3288}" name="Description" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{B6B86EFF-FFA0-4D77-AFEA-220F5D28CE3B}" name="Inconsistency Type" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{AA763C70-26AE-4394-9943-58CCD15D3288}" name="Description" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{BDB3887F-1B89-4CCC-BD22-20AD8832DF71}" name="Suggestion to handle" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{B2980CFB-2825-4221-ADD2-D137041A83AB}" name="Distinct Count of [Row Id]" dataDxfId="0"/>
   </tableColumns>
@@ -597,101 +600,103 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D9" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Project/Solution/Task_5_Inconcistencies_Analysis.xlsx
+++ b/Project/Solution/Task_5_Inconcistencies_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github_windows\DE_CS_202309\Project\Solution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA9962B-06C3-4CAF-8FBA-BE55D74B07B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC4F7EE-44E8-48F0-A9A7-41EA8C5CF937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E28B71DA-33FB-45D9-97D2-4FF5209A988D}"/>
+    <workbookView xWindow="8445" yWindow="3090" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{E28B71DA-33FB-45D9-97D2-4FF5209A988D}"/>
   </bookViews>
   <sheets>
     <sheet name="Inconsistencies_Summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
   <si>
     <t>Inconsistency Type</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>Suggestion to handle</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> &lt;Columns from source files&gt;</t>
   </si>
   <si>
     <t>Distinct Count of [Row Id]</t>
@@ -170,9 +167,6 @@
 separated by "/".</t>
   </si>
   <si>
-    <t xml:space="preserve">The Date format of the Order Dat column was inconsistent with the rest of the data. Also, there are rows which are in mixed DD/MM/YYYY and MM/DD/YYYY format. </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 pair of products have the same ID. In Total, 10 objects have Data consistency isssues. </t>
   </si>
   <si>
@@ -183,13 +177,73 @@
   </si>
   <si>
     <t xml:space="preserve">There are user names that have non-standard characters in it. It can cause issues in some cases while filtering or formatting. </t>
+  </si>
+  <si>
+    <t>1183-[CA-2022-138779]-1/15/2022</t>
+  </si>
+  <si>
+    <t>4165-[US-2022-106131]-1/15/2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Date format of the Order Dat column was inconsistent with the rest of the data. Also, there are rows which are in mixed DD/MM/YYYY and MM/DD/YYYY format. Note: The "/" seems to be specific to 15th Jan every year, so may check if there is any change in the workflow on that date. </t>
+  </si>
+  <si>
+    <t>67-[FUR-CH-10001146], 129-[FUR-CH-10001146]</t>
+  </si>
+  <si>
+    <t>2116-[FUR-BO-10002213],2472-[FUR-BO-10002213]</t>
+  </si>
+  <si>
+    <t>202206_Orders_2022_07_05_18_29_34.csv</t>
+  </si>
+  <si>
+    <t>Example 1 (Row ID / File Name)</t>
+  </si>
+  <si>
+    <t>Example 2 (ROW ID / File Name)</t>
+  </si>
+  <si>
+    <t>There are user names that have non-standard characters in it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> It can cause issues in some cases while filtering or formatting. Names like, Barry FranzÃ¶sisch, Anna HÃ¤berlin, Neil FranzÃ¶sisch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This should be changed at source or the encoding of the file can be unified. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 incorrect names and 48 rows of data. </t>
+  </si>
+  <si>
+    <t>Unique Order IDs</t>
+  </si>
+  <si>
+    <t>Duplicate Products</t>
+  </si>
+  <si>
+    <t>Data Quality</t>
+  </si>
+  <si>
+    <t>Negative Quantity</t>
+  </si>
+  <si>
+    <t>Incorrect Names</t>
+  </si>
+  <si>
+    <t>Total Issues</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is an approx figure, however the actual value will change depending upon what action needs to be taken at the data level, and the weightage given to issues by the management. Some small issues may carry more wright and vice-versa. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,6 +253,33 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -223,22 +304,112 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -266,12 +437,24 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{53DD33C5-2FF4-4D40-B827-D836ACC78D2E}" name="Table1" displayName="Table1" ref="A1:D9" totalsRowShown="0">
   <autoFilter ref="A1:D9" xr:uid="{53DD33C5-2FF4-4D40-B827-D836ACC78D2E}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B6B86EFF-FFA0-4D77-AFEA-220F5D28CE3B}" name="Inconsistency Type" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{AA763C70-26AE-4394-9943-58CCD15D3288}" name="Description" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{BDB3887F-1B89-4CCC-BD22-20AD8832DF71}" name="Suggestion to handle" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{B2980CFB-2825-4221-ADD2-D137041A83AB}" name="Distinct Count of [Row Id]" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B6B86EFF-FFA0-4D77-AFEA-220F5D28CE3B}" name="Inconsistency Type" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{AA763C70-26AE-4394-9943-58CCD15D3288}" name="Description" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{BDB3887F-1B89-4CCC-BD22-20AD8832DF71}" name="Suggestion to handle" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{B2980CFB-2825-4221-ADD2-D137041A83AB}" name="Distinct Count of [Row Id]" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{666FFA8D-86CC-44FE-97DC-8D44FC2958C4}" name="Table3" displayName="Table3" ref="A1:C9" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C9" xr:uid="{666FFA8D-86CC-44FE-97DC-8D44FC2958C4}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{45747B75-4977-4F31-BAAB-7A13DC0F28D3}" name="Inconsistency Type" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{57053A07-1B2F-42CA-9BFE-B99CCCFFDF60}" name="Example 1 (Row ID / File Name)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{874956BF-3F6F-43F4-9075-D40E7BA79740}" name="Example 2 (ROW ID / File Name)" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -572,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CBF323B-060F-481F-A0D4-2BF6515E2300}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" style="1" customWidth="1"/>
@@ -592,111 +775,474 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>29</v>
+      <c r="D3" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -708,31 +1254,225 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1BF7D5B-08CF-4195-ADFA-65D9DB48B98E}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>3</v>
+      <c r="B1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1505</v>
+      </c>
+      <c r="C7" s="4">
+        <v>8168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2372</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3807</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF43279-16C1-4719-94DF-8E075411B9FE}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:E18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <f>SUM(C3:C7)</f>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10">
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="7">
+        <f>(C10-C8)/C10</f>
+        <v>0.91139505655634689</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B15:E18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>